--- a/01_Processing/03_Blood_Correction/c_data/blood_correction.xlsx
+++ b/01_Processing/03_Blood_Correction/c_data/blood_correction.xlsx
@@ -140,7 +140,7 @@
     <t>proteins</t>
   </si>
   <si>
-    <t>01_Processing/02_Quantification/c_data/proteins.rds</t>
+    <t>01_Processing/02_Quantification/c_data/quantification.rds</t>
   </si>
   <si>
     <t>1515aaf05e2e49ec10eb1339362c0f18</t>
